--- a/04-vendor-risk-management/04-vendor-risk-programme.xlsx
+++ b/04-vendor-risk-management/04-vendor-risk-programme.xlsx
@@ -157,13 +157,13 @@
     <t xml:space="preserve">PUBLISHING</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload this .xlsx next to its .md file. GitHub cannot preview .xlsx, so the project README links to it as a download.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notion</t>
+    <t xml:space="preserve">CodeCo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload this .xlsx next to its .md file. CodeCo cannot preview .xlsx, so the project README links to it as a download.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WikiCo</t>
   </si>
   <si>
     <t xml:space="preserve">Import the matching CSV files from the data/ folder (Settings → Import → CSV) for sortable databases.</t>
@@ -250,7 +250,7 @@
     <t xml:space="preserve">CGI-VEN-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+    <t xml:space="preserve">CloudCo</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud hosting and infrastructure for the production platform</t>
@@ -301,7 +301,7 @@
     <t xml:space="preserve">CGI-VEN-002</t>
   </si>
   <si>
-    <t xml:space="preserve">GitHub (Microsoft)</t>
+    <t xml:space="preserve">CodeCo</t>
   </si>
   <si>
     <t xml:space="preserve">Source code hosting, CI/CD pipeline and secrets store</t>
@@ -346,7 +346,7 @@
     <t xml:space="preserve">CGI-VEN-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Google Workspace</t>
+    <t xml:space="preserve">OfficeCo</t>
   </si>
   <si>
     <t xml:space="preserve">Email, documents, shared drives and primary identity provider</t>
@@ -388,7 +388,7 @@
     <t xml:space="preserve">CGI-VEN-004</t>
   </si>
   <si>
-    <t xml:space="preserve">Slack (Salesforce)</t>
+    <t xml:space="preserve">ChatCo</t>
   </si>
   <si>
     <t xml:space="preserve">Internal communications, incident channel and customer-facing shared channels</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">CGI-VEN-005</t>
   </si>
   <si>
-    <t xml:space="preserve">Stripe</t>
+    <t xml:space="preserve">PaymentsCo</t>
   </si>
   <si>
     <t xml:space="preserve">Payment processing and subscription billing</t>
@@ -472,7 +472,7 @@
     <t xml:space="preserve">CGI-VEN-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Auth0 (Okta)</t>
+    <t xml:space="preserve">LoginCo</t>
   </si>
   <si>
     <t xml:space="preserve">Customer identity and authentication for the CGI platform</t>
@@ -511,7 +511,7 @@
     <t xml:space="preserve">CGI-VEN-007</t>
   </si>
   <si>
-    <t xml:space="preserve">Datadog</t>
+    <t xml:space="preserve">MonitorCo</t>
   </si>
   <si>
     <t xml:space="preserve">Application performance monitoring and application log search (engineering use; not configured as a security log source)</t>
@@ -550,7 +550,7 @@
     <t xml:space="preserve">CGI-VEN-008</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot</t>
+    <t xml:space="preserve">CRMCo</t>
   </si>
   <si>
     <t xml:space="preserve">CRM, marketing automation and customer lifecycle management</t>
@@ -592,7 +592,7 @@
     <t xml:space="preserve">CGI-VEN-009</t>
   </si>
   <si>
-    <t xml:space="preserve">Zendesk</t>
+    <t xml:space="preserve">SupportCo</t>
   </si>
   <si>
     <t xml:space="preserve">Customer support ticketing and help centre</t>
@@ -622,7 +622,7 @@
     <t xml:space="preserve">CGI-VEN-010</t>
   </si>
   <si>
-    <t xml:space="preserve">Personio</t>
+    <t xml:space="preserve">HRCo</t>
   </si>
   <si>
     <t xml:space="preserve">HR information system, employee records and onboarding workflow</t>
@@ -679,7 +679,7 @@
     <t xml:space="preserve">CGI-VEN-012</t>
   </si>
   <si>
-    <t xml:space="preserve">Otter.ai</t>
+    <t xml:space="preserve">ScribeCo</t>
   </si>
   <si>
     <t xml:space="preserve">AI meeting transcription and summarisation (joins customer and internal calls)</t>
@@ -721,13 +721,13 @@
     <t xml:space="preserve">CGI-VEN-013</t>
   </si>
   <si>
-    <t xml:space="preserve">Grammarly Business</t>
+    <t xml:space="preserve">WriteCo</t>
   </si>
   <si>
     <t xml:space="preserve">AI writing assistance browser extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Any text typed into any web field, including Slack, Notion, the CGI admin console and email</t>
+    <t xml:space="preserve">Any text typed into any web field, including ChatCo, WikiCo, the CGI admin console and email</t>
   </si>
   <si>
     <t xml:space="preserve">12 seats / Medium</t>
@@ -748,7 +748,7 @@
     <t xml:space="preserve">CGI-VEN-014</t>
   </si>
   <si>
-    <t xml:space="preserve">Figma</t>
+    <t xml:space="preserve">DesignCo</t>
   </si>
   <si>
     <t xml:space="preserve">Product and interface design</t>
@@ -781,7 +781,7 @@
     <t xml:space="preserve">CGI-VEN-015</t>
   </si>
   <si>
-    <t xml:space="preserve">Calendly</t>
+    <t xml:space="preserve">SchedulerCo</t>
   </si>
   <si>
     <t xml:space="preserve">External meeting scheduling</t>
@@ -808,7 +808,7 @@
     <t xml:space="preserve">CGI-VEN-016</t>
   </si>
   <si>
-    <t xml:space="preserve">Miro</t>
+    <t xml:space="preserve">WhiteboardCo</t>
   </si>
   <si>
     <t xml:space="preserve">Collaborative whiteboarding for workshops and architecture sessions</t>
@@ -832,7 +832,7 @@
     <t xml:space="preserve">CGI-VEN-017</t>
   </si>
   <si>
-    <t xml:space="preserve">Atlassian Statuspage</t>
+    <t xml:space="preserve">StatusCo</t>
   </si>
   <si>
     <t xml:space="preserve">Public service status page (required by CGI-GAP-001 REC-14)</t>
@@ -2206,7 +2206,7 @@
     <t xml:space="preserve">VRA-2026-002</t>
   </si>
   <si>
-    <t xml:space="preserve">Slack (CGI-VEN-004)</t>
+    <t xml:space="preserve">ChatCo (CGI-VEN-004)</t>
   </si>
   <si>
     <t xml:space="preserve">FAIL — remediate or exit</t>
@@ -2218,7 +2218,7 @@
     <t xml:space="preserve">VRA-2026-001</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS (CGI-VEN-001)</t>
+    <t xml:space="preserve">CloudCo (CGI-VEN-001)</t>
   </si>
   <si>
     <t xml:space="preserve">PASS WITH CONDITIONS</t>
@@ -2230,7 +2230,7 @@
     <t xml:space="preserve">VRA-2026-003</t>
   </si>
   <si>
-    <t xml:space="preserve">Calendly (CGI-VEN-015)</t>
+    <t xml:space="preserve">SchedulerCo (CGI-VEN-015)</t>
   </si>
   <si>
     <t xml:space="preserve">ACCEPTED — documented justification (ACC-V01)</t>
@@ -2239,10 +2239,10 @@
     <t xml:space="preserve">1 observation</t>
   </si>
   <si>
-    <t xml:space="preserve">Calendly is Tier 3: its Pass band is converted to a documented acceptance with an expiry, per §4.3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slack (VRA-2026-002) — findings</t>
+    <t xml:space="preserve">SchedulerCo is Tier 3: its Pass band is converted to a documented acceptance with an expiry, per §4.3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatCo (VRA-2026-002) — findings</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -2398,7 +2398,7 @@
     <t xml:space="preserve">Accepted as normal commercial practice for a vendor of this size. Recorded, not remediated.</t>
   </si>
   <si>
-    <t xml:space="preserve">Slack — remediation plan</t>
+    <t xml:space="preserve">ChatCo — remediation plan</t>
   </si>
   <si>
     <t xml:space="preserve">Action</t>
@@ -2437,7 +2437,7 @@
     <t xml:space="preserve">Clause in the DPA or an addendum; contact recorded in the inventory</t>
   </si>
   <si>
-    <t xml:space="preserve">R3 Upgrade to a plan supporting SSO federation and SCIM, then federate the workspace to Google Workspace</t>
+    <t xml:space="preserve">R3 Upgrade to a plan supporting SSO federation and SCIM, then federate the workspace to OfficeCo</t>
   </si>
   <si>
     <t xml:space="preserve">15 Nov 2026</t>
@@ -2500,7 +2500,7 @@
     <t xml:space="preserve">CEO decision recorded</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS (VRA-2026-001) — findings</t>
+    <t xml:space="preserve">CloudCo (VRA-2026-001) — findings</t>
   </si>
   <si>
     <t xml:space="preserve">F-010</t>
@@ -2548,7 +2548,7 @@
     <t xml:space="preserve">Confirms CGI-GAP-001 GAP-021 (RC.RP = 1) from the vendor side. An untested backup is an assumption. Closed by REC-03. → VR-007</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS — conditions of the pass</t>
+    <t xml:space="preserve">CloudCo — conditions of the pass</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -2593,7 +2593,7 @@
     <t xml:space="preserve">Dated restore test report and an approved CGI-POL-006</t>
   </si>
   <si>
-    <t xml:space="preserve">Calendly (VRA-2026-003) — observation</t>
+    <t xml:space="preserve">SchedulerCo (VRA-2026-003) — observation</t>
   </si>
   <si>
     <t xml:space="preserve">Observation</t>
@@ -2611,7 +2611,7 @@
     <t xml:space="preserve">Accepted. The data is invitee name, email and subject line, volunteered by the invitee at the point of booking. A compensating configuration change is applied: booking pages must not request free-text detail beyond a subject line, so no Confidential context can be entered into the tool.</t>
   </si>
   <si>
-    <t xml:space="preserve">Calendly — acceptance record ACC-V01</t>
+    <t xml:space="preserve">SchedulerCo — acceptance record ACC-V01</t>
   </si>
   <si>
     <t xml:space="preserve">Field</t>
@@ -2707,7 +2707,7 @@
     <t xml:space="preserve">Personal data processed by a sub-processor under no Article 28 contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Confidential data, including incidental customer personal data, is processed in Slack, Notion, Miro, Otter.ai and Grammarly with no executed Data Processing Agreement, so no processing instructions, no security obligations, no breach-notification pathway and no deletion-on-termination duty exist.</t>
+    <t xml:space="preserve">Confidential data, including incidental customer personal data, is processed in ChatCo, WikiCo, WhiteboardCo, ScribeCo and WriteCo with no executed Data Processing Agreement, so no processing instructions, no security obligations, no breach-notification pathway and no deletion-on-termination duty exist.</t>
   </si>
   <si>
     <t xml:space="preserve">Compliance / Supply chain</t>
@@ -2869,7 +2869,7 @@
     <t xml:space="preserve">Vendor accounts survive employee offboarding, defeating the four-hour revocation SLA</t>
   </si>
   <si>
-    <t xml:space="preserve">A leaver's access is revoked in Google Workspace within the CGI-POL-003 4.5.2 four-hour SLA, but vendor accounts that are not federated to the identity provider and support no automated deprovisioning remain live and reachable with the leaver's own credentials.</t>
+    <t xml:space="preserve">A leaver's access is revoked in OfficeCo within the CGI-POL-003 4.5.2 four-hour SLA, but vendor accounts that are not federated to the identity provider and support no automated deprovisioning remain live and reachable with the leaver's own credentials.</t>
   </si>
   <si>
     <t xml:space="preserve">Access control / Supply chain</t>
@@ -3256,7 +3256,7 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t xml:space="preserve">17 vendors; AWS, GitHub, Slack, Google Workspace and Stripe all present</t>
+    <t xml:space="preserve">17 vendors; CloudCo, CodeCo, ChatCo, OfficeCo and PaymentsCo all present</t>
   </si>
   <si>
     <t xml:space="preserve">All 17 mandated inventory columns present, in the required order, in columns A–Q</t>
@@ -4068,192 +4068,282 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-TPR-001 — Third-Party / Vendor Risk Management Programme v1.0</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIMULATED CASE STUDY. Cypher Group Inc. is a simulated company.</t>
+        </is>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commissioned by</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-GAP-001 REC-15, following GAP-006 (GV.SC = 0).</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>5</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prepared by</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O.S, Assessor</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>7</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approved by</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer — 15 September 2026</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Risk method</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identical NIST SP 800-30 Rev. 1 5 × 5 and thresholds as CGI-RSK-001 v1.0.</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key rule</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tier is decided by your exposure, never by the vendor's quality — and it is decided before any assessment.</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHEETS</t>
+        </is>
       </c>
       <c r="B10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01_Inventory</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17 vendors. Columns A–Q are the 17 mandated inventory columns; R–Z are governance columns. Tier, factor total and rating are formulas.</t>
+        </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>16</v>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02_Tiering_Model</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Factors, escalation triggers, tier rules and a live estate summary.</t>
+        </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>18</v>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03_Questionnaire</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CGI-TPR-002 — 74 questions, 16 domains, weights, evidence and dual mapping. Tier 2 flag is a formula.</t>
+        </is>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>20</v>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04_Assessments</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VRA-2026-001 to -003: scores, bands and decisions are formulas; findings, remediation and conditions below.</t>
+        </is>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>22</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05_Risk_Addendum</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VR-001 to VR-009 with score and rating formulas, plus the CGI-RSK-001 v1.1 merge calculation.</t>
+        </is>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>24</v>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06_KRIs</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KRI-V1 to KRI-V7. KRI-V1 (DPA coverage) is calculated live from the inventory.</t>
+        </is>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>26</v>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07_Clause_Checklist</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 18 contractual security clauses by tier.</t>
+        </is>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>28</v>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08_Issue_Checklist</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality checks performed before issue.</t>
+        </is>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>29</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COLOUR LEGEND</t>
+        </is>
       </c>
       <c r="B20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>31</v>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow cell</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Input — type or choose here</t>
+        </is>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>33</v>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grey cell</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formula — do not overwrite</t>
+        </is>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>35</v>
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pass / compliant / low</t>
+        </is>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>37</v>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amber</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial / condition / medium</t>
+        </is>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>39</v>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fail / non-compliant / high or critical</t>
+        </is>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHING</t>
+        </is>
       </c>
       <c r="B27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>42</v>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GitHub</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload this .xlsx next to its .md file. GitHub cannot preview .xlsx, so the project README links to it as a download.</t>
+        </is>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>44</v>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notion</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import the matching CSV files from the data/ folder (Settings → Import → CSV) for sortable databases.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/04-vendor-risk-management/04-vendor-risk-programme.xlsx
+++ b/04-vendor-risk-management/04-vendor-risk-programme.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Approved by</t>
   </si>
   <si>
-    <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer — 15 September 2026</t>
+    <t xml:space="preserve">Jerry Gold, Chief Executive Officer — 15 September 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Risk method</t>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerry Olugboye, Chief Executive Officer — 15 September 2026</t>
+          <t xml:space="preserve">Jerry Gold, Chief Executive Officer — 15 September 2026</t>
         </is>
       </c>
     </row>
